--- a/output/laminas_comunales/comunal_m_miginterna_a_2020_o_higgins.xlsx
+++ b/output/laminas_comunales/comunal_m_miginterna_a_2020_o_higgins.xlsx
@@ -1095,7 +1095,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2019_2020. Escala de colores estandarizada a nivel nacional para todo el periodo.</t>
+          <t>Periodo 2019_2020. Escala comunal recortada al rango percentil 5-95; los valores fuera de ese rango se muestran saturados y anotados con su valor real.</t>
         </is>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_m_miginterna_a_2020_o_higgins.xlsx
+++ b/output/laminas_comunales/comunal_m_miginterna_a_2020_o_higgins.xlsx
@@ -1095,7 +1095,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2019_2020. Escala comunal recortada al rango percentil 5-95; los valores fuera de ese rango se muestran saturados y anotados con su valor real.</t>
+          <t>Periodo 2019_2020. Escala comunal recortada a percentiles 3-97.</t>
         </is>
       </c>
     </row>
